--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260709.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,185,000</t>
+          <t>9,622,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
@@ -660,24 +660,24 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>43,790,000</t>
+          <t>9,501,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -689,44 +689,44 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>10,293,000</t>
+          <t>43,790,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>9,501,000</t>
+          <t>10,293,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -770,46 +770,46 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>32,516,000</t>
+          <t>4,071,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>4,071,000</t>
+          <t>32,516,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>28,640,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>28,640,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -946,46 +946,46 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,946,000</t>
+          <t>32,659,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>32,659,000</t>
+          <t>1,946,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,66 +997,66 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,532,000</t>
+          <t>13,608,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>8,532,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13,608,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1078,73 +1078,73 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>19,261,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>19,261,000</t>
+          <t>19,313,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,753,679,317</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1166,73 +1166,73 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>16,240,000</t>
+          <t>5,983,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1254,51 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>16,240,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1320,46 +1320,46 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>21,675,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,88 +1371,88 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,334,000</t>
+          <t>21,675,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,771,000</t>
+          <t>3,334,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,771,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1474,29 +1474,29 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>475,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1518,29 +1518,29 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>44,393,000</t>
+          <t>475,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1562,29 +1562,29 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>44,393,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>6,553,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,39 +1635,39 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>6,553,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,100 +1689,100 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,306,977,177</t>
+          <t>1,312,077,177</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,216,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>17,187,000</t>
+          <t>16,216,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>PB_NTD</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES</t>
+          <t>長華電材</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-7,707,185</t>
+          <t>17,187,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>PB_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>PAYABLES</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-5,934,428,934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-4.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
